--- a/data/trans_camb/P44D-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P44D-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-22,57</t>
+          <t>-21,98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-29,19</t>
+          <t>-29,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-27,16</t>
+          <t>-26,88</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-50,71; 25,67</t>
+          <t>-51,86; 24,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 4,47</t>
+          <t>-66,23; 5,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-71,55; -10,0</t>
+          <t>-75,28; -9,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 1,54</t>
+          <t>-64,68; -1,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 3,98</t>
+          <t>-49,92; 3,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,88; -5,88</t>
+          <t>-56,17; -6,96</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-80,99%</t>
+          <t>-78,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-80,34%</t>
+          <t>-81,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-82,16%</t>
+          <t>-81,31%</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,91; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,96; 9,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-93,53; 62,11</t>
+          <t>-92,31; 71,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,63; -42,45</t>
+          <t>-93,12; -40,75</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-3,15</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 0,0</t>
+          <t>-40,74; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 11,55</t>
+          <t>-27,4; 10,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 61,26</t>
+          <t>-16,98; 60,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 8,75</t>
+          <t>-27,84; 7,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 13,42</t>
+          <t>-20,13; 14,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 6,93</t>
+          <t>-20,02; 7,26</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-21,15%</t>
+          <t>-22,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-31,49%</t>
+          <t>-34,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-23,87%</t>
+          <t>-26,04%</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-92,63; —</t>
+          <t>-93,75; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,92; 239,96</t>
+          <t>-78,75; 224,87</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-4,7</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,23</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,39; 24,23</t>
+          <t>-29,21; 24,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 9,02</t>
+          <t>-41,17; 8,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,62</t>
+          <t>0,0; 32,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 17,98</t>
+          <t>4,95; 17,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 19,02</t>
+          <t>-9,52; 18,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 9,8</t>
+          <t>-14,71; 9,56</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-41,68%</t>
+          <t>-42,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-21,82</t>
+          <t>-21,74</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,7</t>
+          <t>-5,9</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 19,45</t>
+          <t>-58,16; 16,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 8,14</t>
+          <t>-64,36; 9,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 35,71</t>
+          <t>-7,47; 36,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 15,8</t>
+          <t>-15,69; 15,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 18,36</t>
+          <t>-24,99; 18,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 7,83</t>
+          <t>-31,0; 8,34</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-69,11%</t>
+          <t>-68,87%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100,43%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,17%</t>
+          <t>-34,33%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-93,55; —</t>
+          <t>-94,9; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,88; —</t>
+          <t>-95,05; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,71; 377,22</t>
+          <t>-81,82; 465,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 177,71</t>
+          <t>-82,46; 188,12</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>-8,15</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>-2,59</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 84,75</t>
+          <t>-32,2; 100,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 11,66</t>
+          <t>-49,3; 11,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1270,17 +1270,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 62,25</t>
+          <t>-15,48; 60,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 7,05</t>
+          <t>-30,55; 8,02</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-51,35%</t>
+          <t>-52,13%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-32,9%</t>
+          <t>-33,88%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-6,09</t>
+          <t>-6,04</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-2,97</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 21,83</t>
+          <t>-31,09; 21,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 6,39</t>
+          <t>-38,68; 6,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 10,86</t>
+          <t>-20,0; 10,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 4,2</t>
+          <t>-24,95; 4,77</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-59,37%</t>
+          <t>-58,88%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-47,07%</t>
+          <t>-46,61%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-37,09</t>
+          <t>-36,9</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-19,37</t>
+          <t>-19,6</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 12,88</t>
+          <t>-37,76; 13,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 17,69</t>
+          <t>-30,69; 18,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-61,23; -12,44</t>
+          <t>-61,78; -9,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-57,71; -10,76</t>
+          <t>-61,05; -13,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-41,92; -6,24</t>
+          <t>-44,37; -6,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-38,9; -3,84</t>
+          <t>-40,66; -3,82</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-83,33%</t>
+          <t>-82,9%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-59,77%</t>
+          <t>-60,5%</t>
         </is>
       </c>
     </row>
@@ -1648,27 +1648,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-75,79; —</t>
+          <t>-68,76; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,87</t>
+          <t>-100,0; 2,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-91,8; -55,58</t>
+          <t>-92,08; -61,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-91,02; -22,84</t>
+          <t>-91,01; -29,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,27; -20,9</t>
+          <t>-79,19; -22,06</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-9,31</t>
+          <t>-9,33</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,82</t>
+          <t>4,11; 35,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,99</t>
+          <t>4,04; 12,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 62,08</t>
+          <t>-13,11; 54,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 5,28</t>
+          <t>-33,34; 5,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,8; 34,2</t>
+          <t>3,45; 36,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 3,53</t>
+          <t>-9,92; 6,59</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-63,6%</t>
+          <t>-63,75%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-37,07%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -1809,22 +1809,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,21; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-90,1; —</t>
+          <t>-91,98; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,42; —</t>
+          <t>-8,0; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-91,96; —</t>
+          <t>-69,25; —</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-10,56</t>
+          <t>-10,65</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-8,49</t>
+          <t>-6,82</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 9,68</t>
+          <t>-9,35; 9,89</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 0,1</t>
+          <t>-12,63; 3,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 3,3</t>
+          <t>-17,08; 3,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -3,74</t>
+          <t>-19,65; -3,56</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,57</t>
+          <t>-9,59; 4,63</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -2,63</t>
+          <t>-13,36; -1,36</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-48,73%</t>
+          <t>-24,45%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-58,93%</t>
+          <t>-59,45%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-55,06%</t>
+          <t>-44,26%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 125,34</t>
+          <t>-52,31; 128,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-82,34; 0,04</t>
+          <t>-59,15; 54,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-73,88; 30,35</t>
+          <t>-71,51; 36,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-74,87; -31,79</t>
+          <t>-74,08; -26,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 39,88</t>
+          <t>-48,34; 45,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-76,61; -28,23</t>
+          <t>-61,48; -12,38</t>
         </is>
       </c>
     </row>
